--- a/research/traditional_assets/database/data/kuwait/kuwait_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09140000000000001</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="E2">
-        <v>0.1655</v>
+        <v>0.103</v>
       </c>
       <c r="G2">
-        <v>0.1179093742507792</v>
+        <v>0.1382185136315486</v>
       </c>
       <c r="H2">
-        <v>0.1179093742507792</v>
+        <v>0.1382185136315486</v>
       </c>
       <c r="I2">
-        <v>0.1957077781963901</v>
+        <v>0.1276440744113438</v>
       </c>
       <c r="J2">
-        <v>0.1909329380361975</v>
+        <v>0.1142833333495185</v>
       </c>
       <c r="K2">
-        <v>249.486</v>
+        <v>143.55</v>
       </c>
       <c r="L2">
-        <v>0.1708983799705449</v>
+        <v>0.05335538664535672</v>
       </c>
       <c r="M2">
-        <v>44.94</v>
+        <v>176.7</v>
       </c>
       <c r="N2">
-        <v>0.02626534190531853</v>
+        <v>0.08797303554269953</v>
       </c>
       <c r="O2">
-        <v>0.1801303479954787</v>
+        <v>1.230929989550679</v>
       </c>
       <c r="P2">
-        <v>42.52</v>
+        <v>157.5</v>
       </c>
       <c r="Q2">
-        <v>0.02485096434833431</v>
+        <v>0.0784139960270242</v>
       </c>
       <c r="R2">
-        <v>0.1704304049125001</v>
+        <v>1.09717868338558</v>
       </c>
       <c r="S2">
-        <v>2.42</v>
+        <v>19.2</v>
       </c>
       <c r="T2">
-        <v>0.05384957721406319</v>
+        <v>0.1086587436332767</v>
       </c>
       <c r="U2">
-        <v>806.8190000000001</v>
+        <v>956.3290000000001</v>
       </c>
       <c r="V2">
-        <v>0.4715482174167154</v>
+        <v>0.4761243073430351</v>
       </c>
       <c r="W2">
-        <v>0.113113735239279</v>
+        <v>0.0716984916559692</v>
       </c>
       <c r="X2">
-        <v>0.04881336106789308</v>
+        <v>0.08269587204126917</v>
       </c>
       <c r="Y2">
-        <v>0.06430037417138597</v>
+        <v>-0.01099738038529997</v>
       </c>
       <c r="Z2">
-        <v>1.644621591143366</v>
+        <v>1.996473733694172</v>
       </c>
       <c r="AA2">
-        <v>0.124314942115382</v>
+        <v>0.1208843308288122</v>
       </c>
       <c r="AB2">
-        <v>0.04881336106789308</v>
+        <v>0.08245732914076984</v>
       </c>
       <c r="AC2">
-        <v>0.07550158104748887</v>
+        <v>0.0384270016880424</v>
       </c>
       <c r="AD2">
-        <v>424.19</v>
+        <v>204.47</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>424.19</v>
+        <v>204.47</v>
       </c>
       <c r="AG2">
-        <v>-382.6290000000001</v>
+        <v>-751.859</v>
       </c>
       <c r="AH2">
-        <v>0.1986661608568792</v>
+        <v>0.09239326898745617</v>
       </c>
       <c r="AI2">
-        <v>0.1794685203440529</v>
+        <v>0.07984084155612912</v>
       </c>
       <c r="AJ2">
-        <v>-0.2880437769267773</v>
+        <v>-0.5982751802124754</v>
       </c>
       <c r="AK2">
-        <v>-0.245783740832788</v>
+        <v>-0.4685527790951372</v>
       </c>
       <c r="AL2">
-        <v>6.99</v>
+        <v>11.797</v>
       </c>
       <c r="AM2">
-        <v>6.99</v>
+        <v>11.797</v>
       </c>
       <c r="AN2">
-        <v>1.424173241564546</v>
+        <v>0.5672001997281478</v>
       </c>
       <c r="AO2">
-        <v>40.87324749642346</v>
+        <v>29.11079087903705</v>
       </c>
       <c r="AP2">
-        <v>-1.284636562027867</v>
+        <v>-2.085658409387223</v>
       </c>
       <c r="AQ2">
-        <v>40.87324749642346</v>
+        <v>29.11079087903705</v>
       </c>
     </row>
     <row r="3">
@@ -722,118 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.171</v>
+        <v>0.27</v>
       </c>
       <c r="E3">
-        <v>0.29</v>
+        <v>-0.103</v>
       </c>
       <c r="G3">
-        <v>0.09407737786536666</v>
+        <v>0.128647666628818</v>
       </c>
       <c r="H3">
-        <v>0.09407737786536666</v>
+        <v>0.128647666628818</v>
       </c>
       <c r="I3">
-        <v>0.2014313867856031</v>
+        <v>0.1155330986715113</v>
       </c>
       <c r="J3">
-        <v>0.1840853039623004</v>
+        <v>0.07183405098746816</v>
       </c>
       <c r="K3">
-        <v>159.2</v>
+        <v>17.3</v>
       </c>
       <c r="L3">
-        <v>0.1651280987449434</v>
+        <v>0.009821732712614965</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.103393085787452</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>5.601156069364162</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.103393085787452</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>5.601156069364162</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>708.6</v>
+        <v>744.6</v>
       </c>
       <c r="V3">
-        <v>0.7059878449735977</v>
+        <v>0.79449423815621</v>
       </c>
       <c r="W3">
-        <v>0.4469399213924761</v>
+        <v>0.02456688440783868</v>
       </c>
       <c r="X3">
-        <v>0.06071330084983306</v>
+        <v>0.0898483340701017</v>
       </c>
       <c r="Y3">
-        <v>0.3862266205426431</v>
+        <v>-0.06528144966226303</v>
       </c>
       <c r="Z3">
-        <v>8.59269162210339</v>
+        <v>7.186454508363934</v>
       </c>
       <c r="AA3">
-        <v>1.581788249109214</v>
+        <v>0.5162321395729352</v>
       </c>
       <c r="AB3">
-        <v>0.05212643935939552</v>
+        <v>0.08280746971827874</v>
       </c>
       <c r="AC3">
-        <v>1.529661809749819</v>
+        <v>0.4334246698546565</v>
       </c>
       <c r="AD3">
-        <v>416.8</v>
+        <v>187.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>416.8</v>
+        <v>187.1</v>
       </c>
       <c r="AG3">
-        <v>-291.8</v>
+        <v>-557.5</v>
       </c>
       <c r="AH3">
-        <v>0.2934178106300598</v>
+        <v>0.1664146580094281</v>
       </c>
       <c r="AI3">
-        <v>0.311486435991331</v>
+        <v>0.1423138358560889</v>
       </c>
       <c r="AJ3">
-        <v>-0.4098890293580559</v>
+        <v>-1.468264419278378</v>
       </c>
       <c r="AK3">
-        <v>-0.4635424940428912</v>
+        <v>-0.9778986142781969</v>
       </c>
       <c r="AL3">
-        <v>6.99</v>
+        <v>11.6</v>
       </c>
       <c r="AM3">
-        <v>6.99</v>
+        <v>11.6</v>
       </c>
       <c r="AN3">
-        <v>2.036150464093796</v>
+        <v>0.8618148318747121</v>
       </c>
       <c r="AO3">
-        <v>27.78254649499284</v>
+        <v>17.54310344827586</v>
       </c>
       <c r="AP3">
-        <v>-1.425500732779678</v>
+        <v>-2.567941040994933</v>
       </c>
       <c r="AQ3">
-        <v>27.78254649499284</v>
+        <v>17.54310344827586</v>
       </c>
     </row>
     <row r="4">
@@ -853,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.123</v>
+        <v>0.125</v>
       </c>
       <c r="E4">
-        <v>0.13</v>
+        <v>0.103</v>
       </c>
       <c r="G4">
-        <v>0.1165109034267913</v>
+        <v>0.1385269121813031</v>
       </c>
       <c r="H4">
-        <v>0.1165109034267913</v>
+        <v>0.1385269121813031</v>
       </c>
       <c r="I4">
-        <v>0.1429906542056075</v>
+        <v>0.1594900849858357</v>
       </c>
       <c r="J4">
-        <v>0.1414896964068033</v>
+        <v>0.1577969474894281</v>
       </c>
       <c r="K4">
-        <v>45.6</v>
+        <v>52.5</v>
       </c>
       <c r="L4">
-        <v>0.1420560747663552</v>
+        <v>0.1487252124645892</v>
       </c>
       <c r="M4">
-        <v>17.5</v>
+        <v>23.2</v>
       </c>
       <c r="N4">
-        <v>0.04836926478717524</v>
+        <v>0.06592782040352373</v>
       </c>
       <c r="O4">
-        <v>0.3837719298245614</v>
+        <v>0.4419047619047619</v>
       </c>
       <c r="P4">
-        <v>17.5</v>
+        <v>23.2</v>
       </c>
       <c r="Q4">
-        <v>0.04836926478717524</v>
+        <v>0.06592782040352373</v>
       </c>
       <c r="R4">
-        <v>0.3837719298245614</v>
+        <v>0.4419047619047619</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,31 +904,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>51.1</v>
+        <v>45.5</v>
       </c>
       <c r="V4">
-        <v>0.1412382531785517</v>
+        <v>0.1292980960500142</v>
       </c>
       <c r="W4">
-        <v>0.1257931034482759</v>
+        <v>0.125</v>
       </c>
       <c r="X4">
-        <v>0.04881336106789308</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="Y4">
-        <v>0.0769797423803828</v>
+        <v>0.04255744280149848</v>
       </c>
       <c r="Z4">
-        <v>0.9547888161808448</v>
+        <v>0.9568988885876932</v>
       </c>
       <c r="AA4">
-        <v>0.1350927797340388</v>
+        <v>0.1509957236751643</v>
       </c>
       <c r="AB4">
-        <v>0.04881336106789308</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AC4">
-        <v>0.08627941866614575</v>
+        <v>0.06855316647666279</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -937,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-51.1</v>
+        <v>-45.5</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -946,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.1644673318313486</v>
+        <v>-0.1484986945169713</v>
       </c>
       <c r="AK4">
-        <v>-0.1258000984736583</v>
+        <v>-0.110732538330494</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -961,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-1.091880341880342</v>
+        <v>-0.801056338028169</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kuwait Insurance Company S.A.K.P. (KWSE:KINS)</t>
+          <t>Gulf Insurance Group (SASE:8250)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,43 +984,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.09140000000000001</v>
+        <v>0.0247</v>
+      </c>
+      <c r="E5">
+        <v>0.141</v>
       </c>
       <c r="G5">
-        <v>0.3692307692307693</v>
+        <v>0.1231749402707725</v>
       </c>
       <c r="H5">
-        <v>0.3692307692307693</v>
+        <v>0.1231749402707725</v>
       </c>
       <c r="I5">
-        <v>0.3805128205128205</v>
+        <v>0.09105388903636846</v>
       </c>
       <c r="J5">
-        <v>0.3767699014881576</v>
+        <v>0.0720420506217367</v>
       </c>
       <c r="K5">
-        <v>36.4</v>
+        <v>27</v>
       </c>
       <c r="L5">
-        <v>0.3733333333333333</v>
+        <v>0.07167507300238918</v>
       </c>
       <c r="M5">
-        <v>20.5</v>
+        <v>13.3</v>
       </c>
       <c r="N5">
-        <v>0.08671742808798646</v>
+        <v>0.0406355025970058</v>
       </c>
       <c r="O5">
-        <v>0.5631868131868132</v>
+        <v>0.4925925925925926</v>
       </c>
       <c r="P5">
-        <v>20.5</v>
+        <v>13.3</v>
       </c>
       <c r="Q5">
-        <v>0.08671742808798646</v>
+        <v>0.0406355025970058</v>
       </c>
       <c r="R5">
-        <v>0.5631868131868132</v>
+        <v>0.4925925925925926</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1026,67 +1032,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>34.9</v>
+        <v>89.8</v>
       </c>
       <c r="V5">
-        <v>0.1476311336717428</v>
+        <v>0.2743660250534677</v>
       </c>
       <c r="W5">
-        <v>0.113113735239279</v>
+        <v>0.1036070606293169</v>
       </c>
       <c r="X5">
-        <v>0.04881336106789308</v>
+        <v>0.08294918688403682</v>
       </c>
       <c r="Y5">
-        <v>0.06430037417138597</v>
+        <v>0.02065787374528012</v>
       </c>
       <c r="Z5">
-        <v>0.3299492385786802</v>
+        <v>1.77412518249894</v>
       </c>
       <c r="AA5">
-        <v>0.124314942115382</v>
+        <v>0.1278116162068865</v>
       </c>
       <c r="AB5">
-        <v>0.04881336106789308</v>
+        <v>0.08247210108303814</v>
       </c>
       <c r="AC5">
-        <v>0.07550158104748887</v>
+        <v>0.04533951512384836</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="AG5">
-        <v>-34.9</v>
+        <v>-85.33</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.01347318925761823</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.01804820931077643</v>
       </c>
       <c r="AJ5">
-        <v>-0.1732009925558313</v>
+        <v>-0.3526470223581435</v>
       </c>
       <c r="AK5">
-        <v>-0.09842075578116186</v>
+        <v>-0.5405080129220244</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.1241666666666667</v>
+      </c>
+      <c r="AO5">
+        <v>174.1116751269035</v>
       </c>
       <c r="AP5">
-        <v>-0.9232804232804233</v>
+        <v>-2.370277777777778</v>
+      </c>
+      <c r="AQ5">
+        <v>174.1116751269035</v>
       </c>
     </row>
     <row r="6">
@@ -1097,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Warba Insurance Company K.S.C.P. (KWSE:WINS)</t>
+          <t>Kuwait Insurance Company S.A.K.P. (KWSE:KINS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1106,103 +1118,103 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.016</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="E6">
-        <v>0.201</v>
+        <v>0.11</v>
       </c>
       <c r="G6">
-        <v>0.1153735632183908</v>
+        <v>0.3327659574468085</v>
       </c>
       <c r="H6">
-        <v>0.1153735632183908</v>
+        <v>0.3327659574468085</v>
       </c>
       <c r="I6">
-        <v>0.114080459770115</v>
+        <v>0.3472340425531915</v>
       </c>
       <c r="J6">
-        <v>0.112770590672621</v>
+        <v>0.3439078154623973</v>
       </c>
       <c r="K6">
-        <v>7.55</v>
+        <v>40</v>
       </c>
       <c r="L6">
-        <v>0.1084770114942529</v>
+        <v>0.3404255319148936</v>
       </c>
       <c r="M6">
-        <v>6.94</v>
+        <v>18.9</v>
       </c>
       <c r="N6">
-        <v>0.07668508287292818</v>
+        <v>0.05984800506649778</v>
       </c>
       <c r="O6">
-        <v>0.919205298013245</v>
+        <v>0.4725</v>
       </c>
       <c r="P6">
-        <v>4.52</v>
+        <v>18.9</v>
       </c>
       <c r="Q6">
-        <v>0.04994475138121546</v>
+        <v>0.05984800506649778</v>
       </c>
       <c r="R6">
-        <v>0.5986754966887416</v>
+        <v>0.4725</v>
       </c>
       <c r="S6">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.3487031700288185</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>12.1</v>
+        <v>44.9</v>
       </c>
       <c r="V6">
-        <v>0.1337016574585635</v>
+        <v>0.1421785940468651</v>
       </c>
       <c r="W6">
-        <v>0.06531141868512111</v>
+        <v>0.1026957637997433</v>
       </c>
       <c r="X6">
-        <v>0.05115336634466623</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="Y6">
-        <v>0.01415805234045488</v>
+        <v>0.02025320660124175</v>
       </c>
       <c r="Z6">
-        <v>0.6615969581749049</v>
+        <v>0.3313592780597857</v>
       </c>
       <c r="AA6">
-        <v>0.07460867976059335</v>
+        <v>0.113957045450738</v>
       </c>
       <c r="AB6">
-        <v>0.04947027155149965</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AC6">
-        <v>0.02513840820909369</v>
+        <v>0.03151448825223643</v>
       </c>
       <c r="AD6">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>-4.71</v>
+        <v>-44.9</v>
       </c>
       <c r="AH6">
-        <v>0.07549290019409541</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.05339981212515355</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.05490150367175661</v>
+        <v>-0.1657438169066076</v>
       </c>
       <c r="AK6">
-        <v>-0.03729511441919392</v>
+        <v>-0.1278837937909428</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1211,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0.8643274853801168</v>
+        <v>0</v>
       </c>
       <c r="AP6">
-        <v>-0.5508771929824561</v>
+        <v>-1.084541062801932</v>
       </c>
     </row>
     <row r="7">
@@ -1234,28 +1246,28 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.117</v>
+        <v>-0.109</v>
       </c>
       <c r="E7">
-        <v>-0.265</v>
+        <v>0.0266</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.3911111111111111</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.3911111111111111</v>
       </c>
       <c r="I7">
-        <v>0.07372549019607842</v>
+        <v>0.4711111111111111</v>
       </c>
       <c r="J7">
-        <v>0.07342619862559366</v>
+        <v>0.4691205007824726</v>
       </c>
       <c r="K7">
-        <v>0.736</v>
+        <v>1.41</v>
       </c>
       <c r="L7">
-        <v>0.09620915032679737</v>
+        <v>0.2088888888888889</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1279,31 +1291,31 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.119</v>
+        <v>0.129</v>
       </c>
       <c r="V7">
-        <v>0.006397849462365591</v>
+        <v>0.01470923603192703</v>
       </c>
       <c r="W7">
-        <v>0.01906735751295337</v>
+        <v>0.03498759305210918</v>
       </c>
       <c r="X7">
-        <v>0.04881336106789308</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="Y7">
-        <v>-0.02974600355493971</v>
+        <v>-0.04745496414639234</v>
       </c>
       <c r="Z7">
-        <v>0.1984384322066872</v>
+        <v>0.1679898459470894</v>
       </c>
       <c r="AA7">
-        <v>0.01457057973815962</v>
+        <v>0.07880748065706902</v>
       </c>
       <c r="AB7">
-        <v>0.04881336106789308</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AC7">
-        <v>-0.03424278132973346</v>
+        <v>-0.003635076541432497</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1315,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-0.119</v>
+        <v>-0.129</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1324,16 +1336,147 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.006439045506195552</v>
+        <v>-0.01492882768198125</v>
       </c>
       <c r="AK7">
-        <v>-0.002961598765585725</v>
+        <v>-0.009869176038558641</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>-0.04056603773584905</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Warba Insurance and Reinsurance Company (K.S.C.P.) (KWSE:WINSRE)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.102</v>
+      </c>
+      <c r="G8">
+        <v>0.1095872170439414</v>
+      </c>
+      <c r="H8">
+        <v>0.1095872170439414</v>
+      </c>
+      <c r="I8">
+        <v>0.0711051930758988</v>
+      </c>
+      <c r="J8">
+        <v>0.06992665396414358</v>
+      </c>
+      <c r="K8">
+        <v>5.34</v>
+      </c>
+      <c r="L8">
+        <v>0.0711051930758988</v>
+      </c>
+      <c r="M8">
+        <v>24.4</v>
+      </c>
+      <c r="N8">
+        <v>0.3609467455621302</v>
+      </c>
+      <c r="O8">
+        <v>4.569288389513108</v>
+      </c>
+      <c r="P8">
+        <v>5.2</v>
+      </c>
+      <c r="Q8">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="R8">
+        <v>0.9737827715355806</v>
+      </c>
+      <c r="S8">
+        <v>19.2</v>
+      </c>
+      <c r="T8">
+        <v>0.7868852459016393</v>
+      </c>
+      <c r="U8">
+        <v>31.4</v>
+      </c>
+      <c r="V8">
+        <v>0.4644970414201184</v>
+      </c>
+      <c r="W8">
+        <v>0.04070121951219512</v>
+      </c>
+      <c r="X8">
+        <v>0.08952156074408688</v>
+      </c>
+      <c r="Y8">
+        <v>-0.04882034123189175</v>
+      </c>
+      <c r="Z8">
+        <v>0.5937228239386513</v>
+      </c>
+      <c r="AA8">
+        <v>0.04151705046017221</v>
+      </c>
+      <c r="AB8">
+        <v>0.0843603770798028</v>
+      </c>
+      <c r="AC8">
+        <v>-0.04284332661963059</v>
+      </c>
+      <c r="AD8">
+        <v>12.9</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>12.9</v>
+      </c>
+      <c r="AG8">
+        <v>-18.5</v>
+      </c>
+      <c r="AH8">
+        <v>0.1602484472049689</v>
+      </c>
+      <c r="AI8">
+        <v>0.09699248120300752</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.3767820773930754</v>
+      </c>
+      <c r="AK8">
+        <v>-0.1820866141732284</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>2.146422628951747</v>
+      </c>
+      <c r="AP8">
+        <v>-3.078202995008319</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07339999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="E2">
-        <v>0.103</v>
+        <v>0.209</v>
       </c>
       <c r="G2">
-        <v>0.1382185136315486</v>
+        <v>0.1606734908905682</v>
       </c>
       <c r="H2">
-        <v>0.1382185136315486</v>
+        <v>0.1606734908905682</v>
       </c>
       <c r="I2">
-        <v>0.1276440744113438</v>
+        <v>0.1437214349012302</v>
       </c>
       <c r="J2">
-        <v>0.1142833333495185</v>
+        <v>0.138490043127524</v>
       </c>
       <c r="K2">
-        <v>143.55</v>
+        <v>328.581</v>
       </c>
       <c r="L2">
-        <v>0.05335538664535672</v>
+        <v>0.1146375416047393</v>
       </c>
       <c r="M2">
-        <v>176.7</v>
+        <v>120.71</v>
       </c>
       <c r="N2">
-        <v>0.08797303554269953</v>
+        <v>0.04759144923079349</v>
       </c>
       <c r="O2">
-        <v>1.230929989550679</v>
+        <v>0.3673675592928379</v>
       </c>
       <c r="P2">
-        <v>157.5</v>
+        <v>111</v>
       </c>
       <c r="Q2">
-        <v>0.0784139960270242</v>
+        <v>0.04376315851725687</v>
       </c>
       <c r="R2">
-        <v>1.09717868338558</v>
+        <v>0.3378162462223926</v>
       </c>
       <c r="S2">
-        <v>19.2</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="T2">
-        <v>0.1086587436332767</v>
+        <v>0.0804407257062381</v>
       </c>
       <c r="U2">
-        <v>956.3290000000001</v>
+        <v>828.075</v>
       </c>
       <c r="V2">
-        <v>0.4761243073430351</v>
+        <v>0.3264790764790765</v>
       </c>
       <c r="W2">
-        <v>0.0716984916559692</v>
+        <v>0.1363738993000677</v>
       </c>
       <c r="X2">
-        <v>0.08269587204126917</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="Y2">
-        <v>-0.01099738038529997</v>
+        <v>0.06252016831144094</v>
       </c>
       <c r="Z2">
-        <v>1.996473733694172</v>
+        <v>2.59279528816224</v>
       </c>
       <c r="AA2">
-        <v>0.1208843308288122</v>
+        <v>0.1583536659703991</v>
       </c>
       <c r="AB2">
-        <v>0.08245732914076984</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="AC2">
-        <v>0.0384270016880424</v>
+        <v>0.0844999349817723</v>
       </c>
       <c r="AD2">
-        <v>204.47</v>
+        <v>206.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>204.47</v>
+        <v>206.7</v>
       </c>
       <c r="AG2">
-        <v>-751.859</v>
+        <v>-621.375</v>
       </c>
       <c r="AH2">
-        <v>0.09239326898745617</v>
+        <v>0.07535325254823047</v>
       </c>
       <c r="AI2">
-        <v>0.07984084155612912</v>
+        <v>0.08515985497692816</v>
       </c>
       <c r="AJ2">
-        <v>-0.5982751802124754</v>
+        <v>-0.3244769595901838</v>
       </c>
       <c r="AK2">
-        <v>-0.4685527790951372</v>
+        <v>-0.3885718752442742</v>
       </c>
       <c r="AL2">
-        <v>11.797</v>
+        <v>25.84</v>
       </c>
       <c r="AM2">
-        <v>11.797</v>
+        <v>25.84</v>
       </c>
       <c r="AN2">
-        <v>0.5672001997281478</v>
+        <v>0.4677528852681602</v>
       </c>
       <c r="AO2">
-        <v>29.11079087903705</v>
+        <v>15.94206656346749</v>
       </c>
       <c r="AP2">
-        <v>-2.085658409387223</v>
+        <v>-1.406143923964698</v>
       </c>
       <c r="AQ2">
-        <v>29.11079087903705</v>
+        <v>15.94206656346749</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.27</v>
+        <v>0.307</v>
       </c>
       <c r="E3">
-        <v>-0.103</v>
+        <v>0.238</v>
       </c>
       <c r="G3">
-        <v>0.128647666628818</v>
+        <v>0.1143499816378994</v>
       </c>
       <c r="H3">
-        <v>0.128647666628818</v>
+        <v>0.1143499816378994</v>
       </c>
       <c r="I3">
-        <v>0.1155330986715113</v>
+        <v>0.08933161953727506</v>
       </c>
       <c r="J3">
-        <v>0.07183405098746816</v>
+        <v>0.07709133477352524</v>
       </c>
       <c r="K3">
-        <v>17.3</v>
+        <v>120.8</v>
       </c>
       <c r="L3">
-        <v>0.009821732712614965</v>
+        <v>0.05545354388542049</v>
       </c>
       <c r="M3">
-        <v>96.90000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="N3">
-        <v>0.103393085787452</v>
+        <v>0.02954048140043764</v>
       </c>
       <c r="O3">
-        <v>5.601156069364162</v>
+        <v>0.4246688741721854</v>
       </c>
       <c r="P3">
-        <v>96.90000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="Q3">
-        <v>0.103393085787452</v>
+        <v>0.02954048140043764</v>
       </c>
       <c r="R3">
-        <v>5.601156069364162</v>
+        <v>0.4246688741721854</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>744.6</v>
+        <v>667.2</v>
       </c>
       <c r="V3">
-        <v>0.79449423815621</v>
+        <v>0.3841990095589082</v>
       </c>
       <c r="W3">
-        <v>0.02456688440783868</v>
+        <v>0.1363738993000677</v>
       </c>
       <c r="X3">
-        <v>0.0898483340701017</v>
+        <v>0.07710164103395964</v>
       </c>
       <c r="Y3">
-        <v>-0.06528144966226303</v>
+        <v>0.0592722582661081</v>
       </c>
       <c r="Z3">
-        <v>7.186454508363934</v>
+        <v>9.888334089877448</v>
       </c>
       <c r="AA3">
-        <v>0.5162321395729352</v>
+        <v>0.7623048736752043</v>
       </c>
       <c r="AB3">
-        <v>0.08280746971827874</v>
+        <v>0.07392831165803716</v>
       </c>
       <c r="AC3">
-        <v>0.4334246698546565</v>
+        <v>0.6883765620171671</v>
       </c>
       <c r="AD3">
-        <v>187.1</v>
+        <v>189.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>187.1</v>
+        <v>189.3</v>
       </c>
       <c r="AG3">
-        <v>-557.5</v>
+        <v>-477.9</v>
       </c>
       <c r="AH3">
-        <v>0.1664146580094281</v>
+        <v>0.09829170777298926</v>
       </c>
       <c r="AI3">
-        <v>0.1423138358560889</v>
+        <v>0.1362458615229596</v>
       </c>
       <c r="AJ3">
-        <v>-1.468264419278378</v>
+        <v>-0.3796774449829189</v>
       </c>
       <c r="AK3">
-        <v>-0.9778986142781969</v>
+        <v>-0.661728053170867</v>
       </c>
       <c r="AL3">
-        <v>11.6</v>
+        <v>21.9</v>
       </c>
       <c r="AM3">
-        <v>11.6</v>
+        <v>21.9</v>
       </c>
       <c r="AN3">
-        <v>0.8618148318747121</v>
+        <v>0.849640933572711</v>
       </c>
       <c r="AO3">
-        <v>17.54310344827586</v>
+        <v>8.885844748858448</v>
       </c>
       <c r="AP3">
-        <v>-2.567941040994933</v>
+        <v>-2.144973070017953</v>
       </c>
       <c r="AQ3">
-        <v>17.54310344827586</v>
+        <v>8.885844748858448</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Al-Ahleia Insurance Company S.A.K.P. (KWSE:AINS)</t>
+          <t>Kuwait Insurance Company S.A.K.P. (KWSE:KINS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.125</v>
+        <v>0.181</v>
       </c>
       <c r="E4">
-        <v>0.103</v>
+        <v>0.375</v>
       </c>
       <c r="G4">
-        <v>0.1385269121813031</v>
+        <v>0.6539888682745826</v>
       </c>
       <c r="H4">
-        <v>0.1385269121813031</v>
+        <v>0.6539888682745826</v>
       </c>
       <c r="I4">
-        <v>0.1594900849858357</v>
+        <v>0.6451762523191095</v>
       </c>
       <c r="J4">
-        <v>0.1577969474894281</v>
+        <v>0.6389915562184469</v>
       </c>
       <c r="K4">
-        <v>52.5</v>
+        <v>136.4</v>
       </c>
       <c r="L4">
-        <v>0.1487252124645892</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="M4">
-        <v>23.2</v>
+        <v>25.5</v>
       </c>
       <c r="N4">
-        <v>0.06592782040352373</v>
+        <v>0.09020162716660772</v>
       </c>
       <c r="O4">
-        <v>0.4419047619047619</v>
+        <v>0.186950146627566</v>
       </c>
       <c r="P4">
-        <v>23.2</v>
+        <v>25.5</v>
       </c>
       <c r="Q4">
-        <v>0.06592782040352373</v>
+        <v>0.09020162716660772</v>
       </c>
       <c r="R4">
-        <v>0.4419047619047619</v>
+        <v>0.186950146627566</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,31 +904,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>45.5</v>
+        <v>114.2</v>
       </c>
       <c r="V4">
-        <v>0.1292980960500142</v>
+        <v>0.403961796957906</v>
       </c>
       <c r="W4">
-        <v>0.125</v>
+        <v>0.3444444444444444</v>
       </c>
       <c r="X4">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="Y4">
-        <v>0.04255744280149848</v>
+        <v>0.2705907134558176</v>
       </c>
       <c r="Z4">
-        <v>0.9568988885876932</v>
+        <v>0.6140700655084022</v>
       </c>
       <c r="AA4">
-        <v>0.1509957236751643</v>
+        <v>0.3923855867863775</v>
       </c>
       <c r="AB4">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="AC4">
-        <v>0.06855316647666279</v>
+        <v>0.3185318557977507</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-45.5</v>
+        <v>-114.2</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -949,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.1484986945169713</v>
+        <v>-0.6777448071216617</v>
       </c>
       <c r="AK4">
-        <v>-0.110732538330494</v>
+        <v>-0.3405905159558604</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.801056338028169</v>
+        <v>-0.8162973552537527</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gulf Insurance Group (SASE:8250)</t>
+          <t>Al-Ahleia Insurance Company S.A.K.P. (KWSE:AINS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,46 +984,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0247</v>
+        <v>0.122</v>
       </c>
       <c r="E5">
-        <v>0.141</v>
+        <v>0.138</v>
       </c>
       <c r="G5">
-        <v>0.1231749402707725</v>
+        <v>0.1540667361835245</v>
       </c>
       <c r="H5">
-        <v>0.1231749402707725</v>
+        <v>0.1540667361835245</v>
       </c>
       <c r="I5">
-        <v>0.09105388903636846</v>
+        <v>0.1684045881126173</v>
       </c>
       <c r="J5">
-        <v>0.0720420506217367</v>
+        <v>0.1665272910648045</v>
       </c>
       <c r="K5">
-        <v>27</v>
+        <v>58.2</v>
       </c>
       <c r="L5">
-        <v>0.07167507300238918</v>
+        <v>0.1517205422314911</v>
       </c>
       <c r="M5">
-        <v>13.3</v>
+        <v>30.1</v>
       </c>
       <c r="N5">
-        <v>0.0406355025970058</v>
+        <v>0.06995119683941436</v>
       </c>
       <c r="O5">
-        <v>0.4925925925925926</v>
+        <v>0.5171821305841925</v>
       </c>
       <c r="P5">
-        <v>13.3</v>
+        <v>30.1</v>
       </c>
       <c r="Q5">
-        <v>0.0406355025970058</v>
+        <v>0.06995119683941436</v>
       </c>
       <c r="R5">
-        <v>0.4925925925925926</v>
+        <v>0.5171821305841925</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1032,73 +1032,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>89.8</v>
+        <v>31.6</v>
       </c>
       <c r="V5">
-        <v>0.2743660250534677</v>
+        <v>0.07343713688124565</v>
       </c>
       <c r="W5">
-        <v>0.1036070606293169</v>
+        <v>0.1373937677053824</v>
       </c>
       <c r="X5">
-        <v>0.08294918688403682</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="Y5">
-        <v>0.02065787374528012</v>
+        <v>0.06354003671675565</v>
       </c>
       <c r="Z5">
-        <v>1.77412518249894</v>
+        <v>0.9509172037679722</v>
       </c>
       <c r="AA5">
-        <v>0.1278116162068865</v>
+        <v>0.1583536659703991</v>
       </c>
       <c r="AB5">
-        <v>0.08247210108303814</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="AC5">
-        <v>0.04533951512384836</v>
+        <v>0.0844999349817723</v>
       </c>
       <c r="AD5">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-85.33</v>
+        <v>-31.6</v>
       </c>
       <c r="AH5">
-        <v>0.01347318925761823</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.01804820931077643</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.3526470223581435</v>
+        <v>-0.07925758715826436</v>
       </c>
       <c r="AK5">
-        <v>-0.5405080129220244</v>
+        <v>-0.07550776583034648</v>
       </c>
       <c r="AL5">
-        <v>0.197</v>
+        <v>3.94</v>
       </c>
       <c r="AM5">
-        <v>0.197</v>
+        <v>3.94</v>
       </c>
       <c r="AN5">
-        <v>0.1241666666666667</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>174.1116751269035</v>
+        <v>16.39593908629442</v>
       </c>
       <c r="AP5">
-        <v>-2.370277777777778</v>
+        <v>-0.4854070660522274</v>
       </c>
       <c r="AQ5">
-        <v>174.1116751269035</v>
+        <v>16.39593908629442</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kuwait Insurance Company S.A.K.P. (KWSE:KINS)</t>
+          <t>Warba Insurance and Reinsurance Company (K.S.C.P.) (KWSE:WINSRE)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1118,103 +1118,103 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.04480000000000001</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="E6">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="G6">
-        <v>0.3327659574468085</v>
+        <v>0.1304863582443654</v>
       </c>
       <c r="H6">
-        <v>0.3327659574468085</v>
+        <v>0.1304863582443654</v>
       </c>
       <c r="I6">
-        <v>0.3472340425531915</v>
+        <v>0.1589561091340451</v>
       </c>
       <c r="J6">
-        <v>0.3439078154623973</v>
+        <v>0.1576941675042786</v>
       </c>
       <c r="K6">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="L6">
-        <v>0.3404255319148936</v>
+        <v>0.1542111506524318</v>
       </c>
       <c r="M6">
-        <v>18.9</v>
+        <v>13.81</v>
       </c>
       <c r="N6">
-        <v>0.05984800506649778</v>
+        <v>0.1765984654731458</v>
       </c>
       <c r="O6">
-        <v>0.4725</v>
+        <v>1.062307692307692</v>
       </c>
       <c r="P6">
-        <v>18.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q6">
-        <v>0.05984800506649778</v>
+        <v>0.05242966751918158</v>
       </c>
       <c r="R6">
-        <v>0.4725</v>
+        <v>0.3153846153846154</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.7031136857349747</v>
       </c>
       <c r="U6">
-        <v>44.9</v>
+        <v>14.8</v>
       </c>
       <c r="V6">
-        <v>0.1421785940468651</v>
+        <v>0.1892583120204604</v>
       </c>
       <c r="W6">
-        <v>0.1026957637997433</v>
+        <v>0.1009316770186335</v>
       </c>
       <c r="X6">
-        <v>0.08244255719850152</v>
+        <v>0.08048345837125839</v>
       </c>
       <c r="Y6">
-        <v>0.02025320660124175</v>
+        <v>0.02044821864737514</v>
       </c>
       <c r="Z6">
-        <v>0.3313592780597857</v>
+        <v>0.7168367346938774</v>
       </c>
       <c r="AA6">
-        <v>0.113957045450738</v>
+        <v>0.1130409721140365</v>
       </c>
       <c r="AB6">
-        <v>0.08244255719850152</v>
+        <v>0.07530390426310993</v>
       </c>
       <c r="AC6">
-        <v>0.03151448825223643</v>
+        <v>0.03773706785092652</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="AG6">
-        <v>-44.9</v>
+        <v>2.599999999999998</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.1820083682008368</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.1390887290167866</v>
       </c>
       <c r="AJ6">
-        <v>-0.1657438169066076</v>
+        <v>0.03217821782178215</v>
       </c>
       <c r="AK6">
-        <v>-0.1278837937909428</v>
+        <v>0.02357207615593833</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1.234042553191489</v>
       </c>
       <c r="AP6">
-        <v>-1.084541062801932</v>
+        <v>0.1843971631205672</v>
       </c>
     </row>
     <row r="7">
@@ -1246,28 +1246,25 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.109</v>
-      </c>
-      <c r="E7">
-        <v>0.0266</v>
+        <v>-0.15</v>
       </c>
       <c r="G7">
-        <v>0.3911111111111111</v>
+        <v>0.07614678899082569</v>
       </c>
       <c r="H7">
-        <v>0.3911111111111111</v>
+        <v>0.07614678899082569</v>
       </c>
       <c r="I7">
-        <v>0.4711111111111111</v>
+        <v>0.05573394495412844</v>
       </c>
       <c r="J7">
-        <v>0.4691205007824726</v>
+        <v>0.05482523932987635</v>
       </c>
       <c r="K7">
-        <v>1.41</v>
+        <v>0.181</v>
       </c>
       <c r="L7">
-        <v>0.2088888888888889</v>
+        <v>0.0415137614678899</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1291,31 +1288,31 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.129</v>
+        <v>0.275</v>
       </c>
       <c r="V7">
-        <v>0.01470923603192703</v>
+        <v>0.03205128205128206</v>
       </c>
       <c r="W7">
-        <v>0.03498759305210918</v>
+        <v>0.01371212121212121</v>
       </c>
       <c r="X7">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="Y7">
-        <v>-0.04745496414639234</v>
+        <v>-0.06014160977650559</v>
       </c>
       <c r="Z7">
-        <v>0.1679898459470894</v>
+        <v>0.3335628490551603</v>
       </c>
       <c r="AA7">
-        <v>0.07880748065706902</v>
+        <v>0.01828766303100458</v>
       </c>
       <c r="AB7">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="AC7">
-        <v>-0.003635076541432497</v>
+        <v>-0.05556606795762221</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1327,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-0.129</v>
+        <v>-0.275</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1336,147 +1333,16 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.01492882768198125</v>
+        <v>-0.03311258278145696</v>
       </c>
       <c r="AK7">
-        <v>-0.009869176038558641</v>
+        <v>-0.02144249512670566</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>-0.04056603773584905</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Kuwait</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Warba Insurance and Reinsurance Company (K.S.C.P.) (KWSE:WINSRE)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.102</v>
-      </c>
-      <c r="G8">
-        <v>0.1095872170439414</v>
-      </c>
-      <c r="H8">
-        <v>0.1095872170439414</v>
-      </c>
-      <c r="I8">
-        <v>0.0711051930758988</v>
-      </c>
-      <c r="J8">
-        <v>0.06992665396414358</v>
-      </c>
-      <c r="K8">
-        <v>5.34</v>
-      </c>
-      <c r="L8">
-        <v>0.0711051930758988</v>
-      </c>
-      <c r="M8">
-        <v>24.4</v>
-      </c>
-      <c r="N8">
-        <v>0.3609467455621302</v>
-      </c>
-      <c r="O8">
-        <v>4.569288389513108</v>
-      </c>
-      <c r="P8">
-        <v>5.2</v>
-      </c>
-      <c r="Q8">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="R8">
-        <v>0.9737827715355806</v>
-      </c>
-      <c r="S8">
-        <v>19.2</v>
-      </c>
-      <c r="T8">
-        <v>0.7868852459016393</v>
-      </c>
-      <c r="U8">
-        <v>31.4</v>
-      </c>
-      <c r="V8">
-        <v>0.4644970414201184</v>
-      </c>
-      <c r="W8">
-        <v>0.04070121951219512</v>
-      </c>
-      <c r="X8">
-        <v>0.08952156074408688</v>
-      </c>
-      <c r="Y8">
-        <v>-0.04882034123189175</v>
-      </c>
-      <c r="Z8">
-        <v>0.5937228239386513</v>
-      </c>
-      <c r="AA8">
-        <v>0.04151705046017221</v>
-      </c>
-      <c r="AB8">
-        <v>0.0843603770798028</v>
-      </c>
-      <c r="AC8">
-        <v>-0.04284332661963059</v>
-      </c>
-      <c r="AD8">
-        <v>12.9</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>12.9</v>
-      </c>
-      <c r="AG8">
-        <v>-18.5</v>
-      </c>
-      <c r="AH8">
-        <v>0.1602484472049689</v>
-      </c>
-      <c r="AI8">
-        <v>0.09699248120300752</v>
-      </c>
-      <c r="AJ8">
-        <v>-0.3767820773930754</v>
-      </c>
-      <c r="AK8">
-        <v>-0.1820866141732284</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>2.146422628951747</v>
-      </c>
-      <c r="AP8">
-        <v>-3.078202995008319</v>
       </c>
     </row>
   </sheetData>
